--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6592" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6592" uniqueCount="774">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+    <t>通用檢驗檢查結果或發現的測量和簡單聲明</t>
+  </si>
+  <si>
+    <t>關於患者的通用檢驗檢查結果測量和簡單聲明，包括由設備或醫護人員觀察到的發現。</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,10 +520,10 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>檢驗檢查的依據</t>
+  </si>
+  <si>
+    <t>產生此檢驗檢查的計畫或請求。</t>
   </si>
   <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -549,10 +549,10 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>作為較大項目的一部分</t>
+  </si>
+  <si>
+    <t>表示此檢驗檢查是其他資源的一部分，例如：用藥給藥、調劑、用藥聲明、處置、免疫接種或影像檢查。</t>
   </si>
   <si>
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
@@ -573,7 +573,7 @@
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
-    <t>The status of the result value.</t>
+    <t>該項檢驗檢查的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -613,10 +613,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>檢驗檢查的分類</t>
+  </si>
+  <si>
+    <t>檢驗檢查的分類。</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -654,7 +654,13 @@
 </t>
   </si>
   <si>
-    <t>此slice綁定的值集之綁定強度雖為最高強度「要求使用(Requird)」，但因slice之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
+    <t>臺灣核心分類</t>
+  </si>
+  <si>
+    <t>臺灣核心檢驗檢查分類。</t>
+  </si>
+  <si>
+    <t>此 slice 綁定的值集之綁定強度雖為最高強度「要求使用 (Requird)」，但因 slice 之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/category-code-tw</t>
@@ -917,13 +923,13 @@
 </t>
   </si>
   <si>
-    <t>概念（Concept）— 參照一個專門術語或只是文字表述</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>檢驗檢查類型</t>
+  </si>
+  <si>
+    <t>描述該檢驗檢查所測量的內容</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -935,14 +941,22 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -979,12 +993,6 @@
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -1100,7 +1108,7 @@
     <t>量測對象</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>檢驗檢查關注的主體 (如患者、群組、設備或位置)。</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -1210,7 +1218,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1221,9 +1229,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1240,10 +1245,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>與此檢驗檢查相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此檢驗檢查是在哪個就醫情境產生的。</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1275,10 +1280,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>檢驗檢查的時間或時段</t>
+  </si>
+  <si>
+    <t>檢驗檢查進行的時間點或時間段。</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -1334,7 +1339,7 @@
     <t>量測人員</t>
   </si>
   <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>執行或負責檢驗檢查的人員。</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -1376,10 +1381,10 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>檢驗檢查的結果值</t>
+  </si>
+  <si>
+    <t>檢驗檢查或觀察的實際結果。</t>
   </si>
   <si>
     <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1439,7 +1444,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1471,7 +1476,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1570,10 +1575,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
+    <t>檢驗檢查的檢體</t>
+  </si>
+  <si>
+    <t>進行檢驗檢查的檢體。</t>
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
@@ -1594,7 +1599,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1674,7 +1679,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1724,7 +1729,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1760,7 +1765,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1801,10 +1806,10 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>包含的相關檢驗檢查</t>
+  </si>
+  <si>
+    <t>與此檢驗檢查相關聯的其他檢驗檢查或問卷回應。</t>
   </si>
   <si>
     <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
@@ -1823,10 +1828,10 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>觀察來源或依據</t>
+  </si>
+  <si>
+    <t>用於獲取此觀察結果的參考資源，如：來源觀察、文件引用、問卷回應等。</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1887,16 +1892,13 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1905,6 +1907,9 @@
   </si>
   <si>
     <t>Actual component result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -2750,7 +2755,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="114.32421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="116.8203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.0625" customWidth="true" bestFit="true"/>
@@ -4612,10 +4617,10 @@
         <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>193</v>
@@ -4649,10 +4654,10 @@
         <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4705,10 +4710,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4731,13 +4736,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4788,7 +4793,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4812,7 +4817,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4823,10 +4828,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4855,7 +4860,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -4896,10 +4901,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4908,7 +4913,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4932,7 +4937,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4943,10 +4948,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4969,19 +4974,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -5030,7 +5035,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -5051,10 +5056,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -5065,10 +5070,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5091,13 +5096,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5148,7 +5153,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -5172,7 +5177,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -5183,10 +5188,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5215,7 +5220,7 @@
         <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>141</v>
@@ -5256,10 +5261,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -5268,7 +5273,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5292,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -5303,10 +5308,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5332,16 +5337,16 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -5351,7 +5356,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -5390,7 +5395,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5411,10 +5416,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5425,10 +5430,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5451,16 +5456,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5510,7 +5515,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5531,10 +5536,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5545,10 +5550,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5574,14 +5579,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5591,7 +5596,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -5630,7 +5635,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5651,10 +5656,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5665,10 +5670,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5691,17 +5696,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5711,7 +5716,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -5750,7 +5755,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5771,10 +5776,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5785,10 +5790,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5811,19 +5816,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5872,7 +5877,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5893,10 +5898,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5907,10 +5912,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5933,19 +5938,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5994,7 +5999,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -6015,10 +6020,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -6029,14 +6034,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -6052,22 +6057,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -6095,10 +6100,10 @@
         <v>116</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -6116,7 +6121,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -6125,36 +6130,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6177,13 +6182,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6234,7 +6239,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6258,7 +6263,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -6269,10 +6274,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6298,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6340,10 +6345,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -6352,7 +6357,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6387,10 +6392,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6410,22 +6415,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6474,7 +6479,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6483,7 +6488,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6495,10 +6500,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6509,10 +6514,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6535,13 +6540,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6592,7 +6597,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6616,7 +6621,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6627,10 +6632,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6656,13 +6661,13 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6700,10 +6705,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6712,7 +6717,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6747,10 +6752,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6776,16 +6781,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6795,7 +6800,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6834,7 +6839,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6855,10 +6860,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6869,10 +6874,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6895,16 +6900,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6954,7 +6959,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6975,10 +6980,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6989,10 +6994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7018,14 +7023,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -7035,7 +7040,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -7074,7 +7079,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7095,10 +7100,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -7109,10 +7114,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7135,17 +7140,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -7155,7 +7160,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -7194,7 +7199,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7215,10 +7220,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -7229,10 +7234,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7255,19 +7260,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -7316,7 +7321,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7337,10 +7342,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7351,10 +7356,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7377,19 +7382,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7438,7 +7443,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7459,10 +7464,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7473,10 +7478,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7499,19 +7504,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7560,7 +7565,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7575,19 +7580,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7595,10 +7600,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7621,13 +7626,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7678,7 +7683,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7702,7 +7707,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7713,10 +7718,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7745,7 +7750,7 @@
         <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>141</v>
@@ -7786,10 +7791,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7798,7 +7803,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7822,7 +7827,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7833,10 +7838,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7859,16 +7864,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7918,7 +7923,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7927,7 +7932,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7953,10 +7958,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7982,13 +7987,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8014,13 +8019,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -8038,7 +8043,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8073,10 +8078,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8102,13 +8107,13 @@
         <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8158,7 +8163,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8182,7 +8187,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -8193,10 +8198,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8219,16 +8224,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8278,7 +8283,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8313,10 +8318,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8339,16 +8344,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8398,7 +8403,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8419,13 +8424,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8433,14 +8438,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8459,19 +8464,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8520,7 +8525,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8535,19 +8540,19 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -8555,14 +8560,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8581,19 +8586,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8642,7 +8647,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8657,19 +8662,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8677,10 +8682,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8703,16 +8708,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8762,7 +8767,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8783,13 +8788,13 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8797,10 +8802,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8823,17 +8828,17 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8882,7 +8887,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8897,19 +8902,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8917,10 +8922,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8943,13 +8948,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -9000,7 +9005,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9024,7 +9029,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -9035,10 +9040,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9067,7 +9072,7 @@
         <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>141</v>
@@ -9108,10 +9113,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -9120,7 +9125,7 @@
         <v>198</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9144,7 +9149,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -9155,10 +9160,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9181,16 +9186,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9240,7 +9245,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9249,7 +9254,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -9275,10 +9280,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9304,13 +9309,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9336,13 +9341,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -9360,7 +9365,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9395,10 +9400,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9424,13 +9429,13 @@
         <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9480,7 +9485,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9504,7 +9509,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9515,10 +9520,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9541,16 +9546,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9600,7 +9605,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9635,10 +9640,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9664,16 +9669,16 @@
         <v>203</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9710,17 +9715,17 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9729,7 +9734,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9738,30 +9743,30 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>20</v>
@@ -9786,16 +9791,16 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9824,7 +9829,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9842,7 +9847,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9851,7 +9856,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9860,27 +9865,27 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9906,16 +9911,16 @@
         <v>203</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9940,13 +9945,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9964,7 +9969,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9973,7 +9978,7 @@
         <v>92</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9988,7 +9993,7 @@
         <v>135</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9999,14 +10004,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10028,16 +10033,16 @@
         <v>203</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -10062,13 +10067,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -10086,7 +10091,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10104,27 +10109,27 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10147,19 +10152,19 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -10208,7 +10213,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10229,10 +10234,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -10243,10 +10248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10272,13 +10277,13 @@
         <v>203</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10304,11 +10309,11 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -10326,7 +10331,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10344,27 +10349,27 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10390,16 +10395,16 @@
         <v>203</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10424,11 +10429,11 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -10446,7 +10451,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10467,10 +10472,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10481,10 +10486,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10507,16 +10512,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10566,7 +10571,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10584,27 +10589,27 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10627,16 +10632,16 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10686,7 +10691,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10704,27 +10709,27 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10747,19 +10752,19 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10808,7 +10813,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10820,7 +10825,7 @@
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
@@ -10829,10 +10834,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10843,10 +10848,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10869,13 +10874,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10926,7 +10931,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10950,7 +10955,7 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10961,10 +10966,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10993,7 +10998,7 @@
         <v>139</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>141</v>
@@ -11046,7 +11051,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -11070,7 +11075,7 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -11081,14 +11086,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11110,10 +11115,10 @@
         <v>138</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>141</v>
@@ -11168,7 +11173,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11203,10 +11208,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11229,13 +11234,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11286,7 +11291,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11295,7 +11300,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -11307,10 +11312,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -11321,10 +11326,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11347,13 +11352,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11404,7 +11409,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11413,7 +11418,7 @@
         <v>92</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>104</v>
@@ -11425,10 +11430,10 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -11439,10 +11444,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11468,16 +11473,16 @@
         <v>203</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11505,10 +11510,10 @@
         <v>116</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -11526,7 +11531,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11544,13 +11549,13 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11561,10 +11566,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11590,16 +11595,16 @@
         <v>203</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11624,13 +11629,13 @@
         <v>20</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>20</v>
@@ -11648,7 +11653,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11666,13 +11671,13 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11683,10 +11688,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11709,17 +11714,17 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11768,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11792,7 +11797,7 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11803,10 +11808,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11829,13 +11834,13 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11886,7 +11891,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11907,10 +11912,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11921,10 +11926,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11947,16 +11952,16 @@
         <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12006,7 +12011,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -12027,10 +12032,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -12041,10 +12046,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12067,16 +12072,16 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12126,7 +12131,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12147,10 +12152,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -12161,10 +12166,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12172,7 +12177,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>81</v>
@@ -12187,19 +12192,19 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -12236,10 +12241,10 @@
         <v>20</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>20</v>
@@ -12248,7 +12253,7 @@
         <v>198</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12269,10 +12274,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -12283,10 +12288,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12309,13 +12314,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12366,7 +12371,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12390,7 +12395,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12401,10 +12406,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12433,7 +12438,7 @@
         <v>139</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>141</v>
@@ -12486,7 +12491,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12510,7 +12515,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12521,14 +12526,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12550,10 +12555,10 @@
         <v>138</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>141</v>
@@ -12608,7 +12613,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12643,10 +12648,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12672,16 +12677,16 @@
         <v>203</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12706,13 +12711,13 @@
         <v>20</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>295</v>
+        <v>602</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -12730,7 +12735,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>92</v>
@@ -12748,16 +12753,16 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>602</v>
+        <v>302</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>20</v>
@@ -12765,10 +12770,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12791,19 +12796,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12852,7 +12857,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12870,27 +12875,27 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12916,16 +12921,16 @@
         <v>203</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12950,13 +12955,13 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -12974,7 +12979,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12983,7 +12988,7 @@
         <v>92</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>104</v>
@@ -12998,7 +13003,7 @@
         <v>135</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -13009,14 +13014,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -13038,16 +13043,16 @@
         <v>203</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -13072,13 +13077,13 @@
         <v>20</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>20</v>
@@ -13096,7 +13101,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13114,27 +13119,27 @@
         <v>20</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13160,16 +13165,16 @@
         <v>82</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -13218,7 +13223,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13239,10 +13244,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -13253,13 +13258,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>20</v>
@@ -13281,19 +13286,19 @@
         <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -13342,7 +13347,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13363,10 +13368,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13377,10 +13382,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13403,13 +13408,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13460,7 +13465,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13484,7 +13489,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13495,10 +13500,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13527,7 +13532,7 @@
         <v>139</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>141</v>
@@ -13580,7 +13585,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13604,7 +13609,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13615,14 +13620,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13644,10 +13649,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>141</v>
@@ -13702,7 +13707,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13737,10 +13742,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13766,16 +13771,16 @@
         <v>203</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13800,13 +13805,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>295</v>
+        <v>602</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13824,7 +13829,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>92</v>
@@ -13842,16 +13847,16 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>602</v>
+        <v>302</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>20</v>
@@ -13859,10 +13864,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13885,13 +13890,13 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13942,7 +13947,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13966,7 +13971,7 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13977,10 +13982,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14009,7 +14014,7 @@
         <v>139</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>141</v>
@@ -14050,10 +14055,10 @@
         <v>20</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>20</v>
@@ -14062,7 +14067,7 @@
         <v>198</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14086,7 +14091,7 @@
         <v>20</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -14097,10 +14102,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14123,19 +14128,19 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -14184,7 +14189,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14205,10 +14210,10 @@
         <v>20</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -14219,10 +14224,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14245,13 +14250,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14302,7 +14307,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14326,7 +14331,7 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14337,10 +14342,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14369,7 +14374,7 @@
         <v>139</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>141</v>
@@ -14410,10 +14415,10 @@
         <v>20</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>20</v>
@@ -14422,7 +14427,7 @@
         <v>198</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14446,7 +14451,7 @@
         <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14457,10 +14462,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14486,16 +14491,16 @@
         <v>106</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -14505,7 +14510,7 @@
         <v>20</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>20</v>
@@ -14544,7 +14549,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14565,10 +14570,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14579,10 +14584,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14605,16 +14610,16 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14664,7 +14669,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14685,10 +14690,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14699,10 +14704,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14728,14 +14733,14 @@
         <v>112</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -14745,7 +14750,7 @@
         <v>20</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>20</v>
@@ -14784,7 +14789,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14805,10 +14810,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14819,10 +14824,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14845,17 +14850,17 @@
         <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14865,7 +14870,7 @@
         <v>20</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>20</v>
@@ -14904,7 +14909,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14925,10 +14930,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14939,10 +14944,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14965,19 +14970,19 @@
         <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -15026,7 +15031,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15047,10 +15052,10 @@
         <v>20</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
@@ -15061,10 +15066,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15087,19 +15092,19 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -15148,7 +15153,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15169,10 +15174,10 @@
         <v>20</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>20</v>
@@ -15183,10 +15188,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15209,19 +15214,19 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -15258,7 +15263,7 @@
         <v>20</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
@@ -15268,7 +15273,7 @@
         <v>198</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15286,30 +15291,30 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>20</v>
@@ -15331,19 +15336,19 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
@@ -15392,7 +15397,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15410,27 +15415,27 @@
         <v>20</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15453,13 +15458,13 @@
         <v>20</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15510,7 +15515,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15534,7 +15539,7 @@
         <v>20</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>20</v>
@@ -15545,10 +15550,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15577,7 +15582,7 @@
         <v>139</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>141</v>
@@ -15618,10 +15623,10 @@
         <v>20</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>20</v>
@@ -15630,7 +15635,7 @@
         <v>198</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15654,7 +15659,7 @@
         <v>20</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>20</v>
@@ -15665,10 +15670,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15691,19 +15696,19 @@
         <v>93</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>20</v>
@@ -15752,7 +15757,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15773,10 +15778,10 @@
         <v>20</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>20</v>
@@ -15787,10 +15792,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15816,20 +15821,20 @@
         <v>112</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q109" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="R109" t="s" s="2">
         <v>20</v>
@@ -15853,10 +15858,10 @@
         <v>181</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>20</v>
@@ -15874,7 +15879,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15895,10 +15900,10 @@
         <v>20</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>20</v>
@@ -15909,10 +15914,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15935,17 +15940,17 @@
         <v>93</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -15994,7 +15999,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -16015,10 +16020,10 @@
         <v>20</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>20</v>
@@ -16029,10 +16034,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16058,14 +16063,14 @@
         <v>106</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -16075,7 +16080,7 @@
         <v>20</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>20</v>
@@ -16114,7 +16119,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16123,7 +16128,7 @@
         <v>92</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>104</v>
@@ -16135,10 +16140,10 @@
         <v>20</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>20</v>
@@ -16149,10 +16154,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16178,16 +16183,16 @@
         <v>112</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -16197,7 +16202,7 @@
         <v>20</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>20</v>
@@ -16236,7 +16241,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16257,10 +16262,10 @@
         <v>20</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>20</v>
@@ -16271,10 +16276,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16300,16 +16305,16 @@
         <v>203</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -16334,13 +16339,13 @@
         <v>20</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>20</v>
@@ -16358,7 +16363,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16367,7 +16372,7 @@
         <v>92</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>104</v>
@@ -16382,7 +16387,7 @@
         <v>135</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>20</v>
@@ -16393,14 +16398,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16422,16 +16427,16 @@
         <v>203</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -16456,13 +16461,13 @@
         <v>20</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>20</v>
@@ -16480,7 +16485,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16498,27 +16503,27 @@
         <v>20</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16544,16 +16549,16 @@
         <v>82</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -16602,7 +16607,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16623,10 +16628,10 @@
         <v>20</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>20</v>
@@ -16637,13 +16642,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>20</v>
@@ -16665,19 +16670,19 @@
         <v>93</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -16726,7 +16731,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16747,10 +16752,10 @@
         <v>20</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>20</v>
@@ -16761,10 +16766,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16787,13 +16792,13 @@
         <v>20</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16844,7 +16849,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16868,7 +16873,7 @@
         <v>20</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>20</v>
@@ -16879,10 +16884,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16911,7 +16916,7 @@
         <v>139</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>141</v>
@@ -16964,7 +16969,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16988,7 +16993,7 @@
         <v>20</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>20</v>
@@ -16999,14 +17004,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17028,10 +17033,10 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>141</v>
@@ -17086,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17121,10 +17126,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17150,16 +17155,16 @@
         <v>203</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>20</v>
@@ -17184,13 +17189,13 @@
         <v>20</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>295</v>
+        <v>602</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>20</v>
@@ -17208,7 +17213,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>92</v>
@@ -17226,16 +17231,16 @@
         <v>20</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>602</v>
+        <v>302</v>
       </c>
       <c r="AP120" t="s" s="2">
         <v>20</v>
@@ -17243,10 +17248,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17269,13 +17274,13 @@
         <v>20</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17326,7 +17331,7 @@
         <v>20</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17350,7 +17355,7 @@
         <v>20</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>20</v>
@@ -17361,10 +17366,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17393,7 +17398,7 @@
         <v>139</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>141</v>
@@ -17434,10 +17439,10 @@
         <v>20</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>20</v>
@@ -17446,7 +17451,7 @@
         <v>198</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17470,7 +17475,7 @@
         <v>20</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>20</v>
@@ -17481,10 +17486,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17507,19 +17512,19 @@
         <v>93</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -17568,7 +17573,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17589,10 +17594,10 @@
         <v>20</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>20</v>
@@ -17603,10 +17608,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17629,13 +17634,13 @@
         <v>20</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17686,7 +17691,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17710,7 +17715,7 @@
         <v>20</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>20</v>
@@ -17721,10 +17726,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17753,7 +17758,7 @@
         <v>139</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>141</v>
@@ -17794,10 +17799,10 @@
         <v>20</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>20</v>
@@ -17806,7 +17811,7 @@
         <v>198</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17830,7 +17835,7 @@
         <v>20</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>20</v>
@@ -17841,10 +17846,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17870,16 +17875,16 @@
         <v>106</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>20</v>
@@ -17889,7 +17894,7 @@
         <v>20</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>20</v>
@@ -17928,7 +17933,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17949,10 +17954,10 @@
         <v>20</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>20</v>
@@ -17963,10 +17968,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17989,16 +17994,16 @@
         <v>93</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -18048,7 +18053,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -18069,10 +18074,10 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>20</v>
@@ -18083,10 +18088,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18112,14 +18117,14 @@
         <v>112</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -18129,7 +18134,7 @@
         <v>20</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>20</v>
@@ -18168,7 +18173,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18189,10 +18194,10 @@
         <v>20</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>20</v>
@@ -18203,10 +18208,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18229,17 +18234,17 @@
         <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
@@ -18249,7 +18254,7 @@
         <v>20</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>20</v>
@@ -18288,7 +18293,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18309,10 +18314,10 @@
         <v>20</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>20</v>
@@ -18323,10 +18328,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18349,19 +18354,19 @@
         <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -18410,7 +18415,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18431,10 +18436,10 @@
         <v>20</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>20</v>
@@ -18445,10 +18450,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18471,19 +18476,19 @@
         <v>93</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -18532,7 +18537,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18553,10 +18558,10 @@
         <v>20</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>20</v>
@@ -18567,10 +18572,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18593,19 +18598,19 @@
         <v>93</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -18642,7 +18647,7 @@
         <v>20</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -18652,7 +18657,7 @@
         <v>198</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18670,30 +18675,30 @@
         <v>20</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>20</v>
@@ -18715,19 +18720,19 @@
         <v>93</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>20</v>
@@ -18776,7 +18781,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18794,27 +18799,27 @@
         <v>20</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP133" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18837,13 +18842,13 @@
         <v>20</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18894,7 +18899,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18918,7 +18923,7 @@
         <v>20</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>20</v>
@@ -18929,10 +18934,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18961,7 +18966,7 @@
         <v>139</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>141</v>
@@ -19002,10 +19007,10 @@
         <v>20</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>20</v>
@@ -19014,7 +19019,7 @@
         <v>198</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19038,7 +19043,7 @@
         <v>20</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>20</v>
@@ -19049,10 +19054,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19075,19 +19080,19 @@
         <v>93</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>20</v>
@@ -19136,7 +19141,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19157,10 +19162,10 @@
         <v>20</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>20</v>
@@ -19171,10 +19176,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19200,20 +19205,20 @@
         <v>112</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q137" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="R137" t="s" s="2">
         <v>20</v>
@@ -19237,10 +19242,10 @@
         <v>181</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>20</v>
@@ -19258,7 +19263,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19279,10 +19284,10 @@
         <v>20</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>20</v>
@@ -19293,10 +19298,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19319,17 +19324,17 @@
         <v>93</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -19378,7 +19383,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19399,10 +19404,10 @@
         <v>20</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>20</v>
@@ -19413,10 +19418,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19442,14 +19447,14 @@
         <v>106</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -19459,7 +19464,7 @@
         <v>20</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>20</v>
@@ -19498,7 +19503,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19507,7 +19512,7 @@
         <v>92</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>104</v>
@@ -19519,10 +19524,10 @@
         <v>20</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>20</v>
@@ -19533,10 +19538,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19562,16 +19567,16 @@
         <v>112</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -19581,7 +19586,7 @@
         <v>20</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>20</v>
@@ -19620,7 +19625,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19641,10 +19646,10 @@
         <v>20</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>20</v>
@@ -19655,10 +19660,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19684,16 +19689,16 @@
         <v>203</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -19718,13 +19723,13 @@
         <v>20</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -19742,7 +19747,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19751,7 +19756,7 @@
         <v>92</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>104</v>
@@ -19766,7 +19771,7 @@
         <v>135</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>20</v>
@@ -19777,14 +19782,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -19806,16 +19811,16 @@
         <v>203</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -19840,13 +19845,13 @@
         <v>20</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>20</v>
@@ -19864,7 +19869,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19882,27 +19887,27 @@
         <v>20</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19928,16 +19933,16 @@
         <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>20</v>
@@ -19986,7 +19991,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20007,10 +20012,10 @@
         <v>20</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>20</v>
@@ -20021,13 +20026,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>20</v>
@@ -20049,19 +20054,19 @@
         <v>93</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -20110,7 +20115,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20131,10 +20136,10 @@
         <v>20</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>20</v>
@@ -20145,10 +20150,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20171,13 +20176,13 @@
         <v>20</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20228,7 +20233,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20252,7 +20257,7 @@
         <v>20</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>20</v>
@@ -20263,10 +20268,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20295,7 +20300,7 @@
         <v>139</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>141</v>
@@ -20348,7 +20353,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20372,7 +20377,7 @@
         <v>20</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>20</v>
@@ -20383,14 +20388,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20412,10 +20417,10 @@
         <v>138</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N147" t="s" s="2">
         <v>141</v>
@@ -20470,7 +20475,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20505,10 +20510,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20534,16 +20539,16 @@
         <v>203</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>20</v>
@@ -20568,13 +20573,13 @@
         <v>20</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>295</v>
+        <v>602</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>20</v>
@@ -20592,7 +20597,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>92</v>
@@ -20610,16 +20615,16 @@
         <v>20</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>601</v>
+        <v>301</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>602</v>
+        <v>302</v>
       </c>
       <c r="AP148" t="s" s="2">
         <v>20</v>
@@ -20627,10 +20632,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20653,13 +20658,13 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20710,7 +20715,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20734,7 +20739,7 @@
         <v>20</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>20</v>
@@ -20745,10 +20750,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20777,7 +20782,7 @@
         <v>139</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>141</v>
@@ -20818,10 +20823,10 @@
         <v>20</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>20</v>
@@ -20830,7 +20835,7 @@
         <v>198</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20854,7 +20859,7 @@
         <v>20</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>20</v>
@@ -20865,10 +20870,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20891,19 +20896,19 @@
         <v>93</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -20952,7 +20957,7 @@
         <v>20</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20973,10 +20978,10 @@
         <v>20</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>20</v>
@@ -20987,10 +20992,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21013,13 +21018,13 @@
         <v>20</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21070,7 +21075,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -21094,7 +21099,7 @@
         <v>20</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>20</v>
@@ -21105,10 +21110,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21137,7 +21142,7 @@
         <v>139</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>141</v>
@@ -21178,10 +21183,10 @@
         <v>20</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>20</v>
@@ -21190,7 +21195,7 @@
         <v>198</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21214,7 +21219,7 @@
         <v>20</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>20</v>
@@ -21225,10 +21230,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21254,16 +21259,16 @@
         <v>106</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>20</v>
@@ -21273,7 +21278,7 @@
         <v>20</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>20</v>
@@ -21312,7 +21317,7 @@
         <v>20</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21333,10 +21338,10 @@
         <v>20</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>20</v>
@@ -21347,10 +21352,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21373,16 +21378,16 @@
         <v>93</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21432,7 +21437,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21453,10 +21458,10 @@
         <v>20</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>20</v>
@@ -21467,10 +21472,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21496,14 +21501,14 @@
         <v>112</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -21513,7 +21518,7 @@
         <v>20</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>20</v>
@@ -21552,7 +21557,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21573,10 +21578,10 @@
         <v>20</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>20</v>
@@ -21587,10 +21592,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21613,17 +21618,17 @@
         <v>93</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>20</v>
@@ -21633,7 +21638,7 @@
         <v>20</v>
       </c>
       <c r="S157" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="T157" t="s" s="2">
         <v>20</v>
@@ -21672,7 +21677,7 @@
         <v>20</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21693,10 +21698,10 @@
         <v>20</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>20</v>
@@ -21707,10 +21712,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21733,19 +21738,19 @@
         <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>20</v>
@@ -21794,7 +21799,7 @@
         <v>20</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21815,10 +21820,10 @@
         <v>20</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>20</v>
@@ -21829,10 +21834,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21855,19 +21860,19 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -21916,7 +21921,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21937,10 +21942,10 @@
         <v>20</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>20</v>
@@ -21951,10 +21956,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21977,19 +21982,19 @@
         <v>93</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>20</v>
@@ -22026,7 +22031,7 @@
         <v>20</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
@@ -22036,7 +22041,7 @@
         <v>198</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -22054,30 +22059,30 @@
         <v>20</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>20</v>
@@ -22099,19 +22104,19 @@
         <v>93</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>439</v>
+        <v>607</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -22160,7 +22165,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22178,27 +22183,27 @@
         <v>20</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22221,13 +22226,13 @@
         <v>20</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22278,7 +22283,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22302,7 +22307,7 @@
         <v>20</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>20</v>
@@ -22313,10 +22318,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22345,7 +22350,7 @@
         <v>139</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>141</v>
@@ -22386,10 +22391,10 @@
         <v>20</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>20</v>
@@ -22398,7 +22403,7 @@
         <v>198</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22422,7 +22427,7 @@
         <v>20</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>20</v>
@@ -22433,10 +22438,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22459,19 +22464,19 @@
         <v>93</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>20</v>
@@ -22520,7 +22525,7 @@
         <v>20</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22541,10 +22546,10 @@
         <v>20</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>20</v>
@@ -22555,10 +22560,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22584,20 +22589,20 @@
         <v>112</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q165" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="R165" t="s" s="2">
         <v>20</v>
@@ -22621,10 +22626,10 @@
         <v>181</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>20</v>
@@ -22642,7 +22647,7 @@
         <v>20</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22663,10 +22668,10 @@
         <v>20</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>20</v>
@@ -22677,10 +22682,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22703,17 +22708,17 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>20</v>
@@ -22762,7 +22767,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22783,10 +22788,10 @@
         <v>20</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>20</v>
@@ -22797,10 +22802,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22826,14 +22831,14 @@
         <v>106</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -22843,7 +22848,7 @@
         <v>20</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>20</v>
@@ -22882,7 +22887,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22891,7 +22896,7 @@
         <v>92</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>104</v>
@@ -22903,10 +22908,10 @@
         <v>20</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>20</v>
@@ -22917,10 +22922,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22946,16 +22951,16 @@
         <v>112</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -22965,7 +22970,7 @@
         <v>20</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>20</v>
@@ -23004,7 +23009,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23025,10 +23030,10 @@
         <v>20</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>20</v>
@@ -23039,10 +23044,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23068,16 +23073,16 @@
         <v>203</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -23102,13 +23107,13 @@
         <v>20</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>20</v>
@@ -23126,7 +23131,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23135,7 +23140,7 @@
         <v>92</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>104</v>
@@ -23150,7 +23155,7 @@
         <v>135</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>20</v>
@@ -23161,14 +23166,14 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -23190,16 +23195,16 @@
         <v>203</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -23224,13 +23229,13 @@
         <v>20</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>20</v>
@@ -23248,7 +23253,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -23266,27 +23271,27 @@
         <v>20</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP170" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23312,16 +23317,16 @@
         <v>82</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>20</v>
@@ -23370,7 +23375,7 @@
         <v>20</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23391,10 +23396,10 @@
         <v>20</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitType.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
